--- a/experiments/results/resnet18/CIFAR-10/baseline/msp/adaptive/max/results.xlsx
+++ b/experiments/results/resnet18/CIFAR-10/baseline/msp/adaptive/max/results.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="33620" yWindow="7360" windowWidth="30240" windowHeight="17260" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="33620" yWindow="4340" windowWidth="30240" windowHeight="17260" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
@@ -65,14 +65,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -353,368 +353,417 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
+    <col width="61.33203125" customWidth="1" style="4" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="3">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="4">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>SVHN</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Places365</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>iSUN</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Texture</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>LSUN</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>LSUN-r</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Average</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1" s="3">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="15.75" customHeight="1" s="4">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>FPR95</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>AUROC</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>FPR95</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>AUROC</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>FPR95</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>AUROC</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>FPR95</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>AUROC</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>FPR95</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>AUROC</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>FPR95</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>AUROC</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>FPR95</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>AUROC</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="n">
+    <row r="3" ht="13" customHeight="1" s="4">
+      <c r="A3" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="2" t="n">
         <v>97.92</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="2" t="n">
         <v>53.08</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="2" t="n">
         <v>90.28</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="2" t="n">
         <v>26.99</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="2" t="n">
         <v>96.16</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="2" t="n">
         <v>23.05</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="2" t="n">
         <v>96.43000000000001</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="2" t="n">
         <v>3.96</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="2" t="n">
         <v>98.95999999999999</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="K3" s="2" t="n">
         <v>28.65</v>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="L3" s="2" t="n">
         <v>95.98</v>
       </c>
-      <c r="M3" s="5" t="n">
+      <c r="M3" s="2" t="n">
         <v>24.46</v>
       </c>
-      <c r="N3" s="5" t="n">
+      <c r="N3" s="2" t="n">
         <v>95.95999999999999</v>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=None,scale_th=3.0,type=max</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="n">
+    <row r="4" ht="13" customHeight="1" s="4">
+      <c r="A4" s="2" t="n">
         <v>12.79</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="2" t="n">
         <v>97.78</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="2" t="n">
         <v>55.96</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="2" t="n">
         <v>88.86</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="2" t="n">
         <v>31.7</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="2" t="n">
         <v>95.73999999999999</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="2" t="n">
         <v>26.06</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="2" t="n">
         <v>96.06</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="2" t="n">
         <v>5.34</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="J4" s="2" t="n">
         <v>98.84</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="K4" s="2" t="n">
         <v>33.21</v>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="L4" s="2" t="n">
         <v>95.5</v>
       </c>
-      <c r="M4" s="5" t="n">
+      <c r="M4" s="2" t="n">
         <v>27.51</v>
       </c>
-      <c r="N4" s="5" t="n">
+      <c r="N4" s="2" t="n">
         <v>95.45999999999999</v>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=None,scale_th=2.0,type=max</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
+    <row r="5" ht="13" customHeight="1" s="4">
+      <c r="A5" s="2" t="n">
         <v>11.63</v>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="2" t="n">
         <v>97.87</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="2" t="n">
         <v>54.24</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="2" t="n">
         <v>89.83</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="2" t="n">
         <v>28.49</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="2" t="n">
         <v>96.03</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="2" t="n">
         <v>24.08</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="2" t="n">
         <v>96.31</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="2" t="n">
         <v>4.32</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="2" t="n">
         <v>98.92</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="K5" s="2" t="n">
         <v>30.05</v>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="L5" s="2" t="n">
         <v>95.83</v>
       </c>
-      <c r="M5" s="5" t="n">
+      <c r="M5" s="2" t="n">
         <v>25.47</v>
       </c>
-      <c r="N5" s="5" t="n">
+      <c r="N5" s="2" t="n">
         <v>95.8</v>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=None,scale_th=2.5,type=max</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="n">
+    <row r="6" ht="13" customHeight="1" s="4">
+      <c r="A6" s="2" t="n">
         <v>10.81</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="2" t="n">
         <v>97.95</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="2" t="n">
         <v>52.48</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="2" t="n">
         <v>90.5</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="2" t="n">
         <v>26.29</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="2" t="n">
         <v>96.23</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="2" t="n">
         <v>22.59</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="2" t="n">
         <v>96.48999999999999</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="2" t="n">
         <v>3.78</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="J6" s="2" t="n">
         <v>98.98</v>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="K6" s="2" t="n">
         <v>28.01</v>
       </c>
-      <c r="L6" s="5" t="n">
+      <c r="L6" s="2" t="n">
         <v>96.06</v>
       </c>
-      <c r="M6" s="5" t="n">
+      <c r="M6" s="2" t="n">
         <v>23.99</v>
       </c>
-      <c r="N6" s="5" t="n">
+      <c r="N6" s="2" t="n">
         <v>96.03</v>
       </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=None,scale_th=3.5,type=max</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
+    <row r="7" ht="13" customHeight="1" s="4">
+      <c r="A7" s="2" t="n">
         <v>10.69</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="2" t="n">
         <v>97.95999999999999</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="2" t="n">
         <v>52.24</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="2" t="n">
         <v>90.61</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="2" t="n">
         <v>26.03</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="2" t="n">
         <v>96.26000000000001</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="2" t="n">
         <v>22.41</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="2" t="n">
         <v>96.52</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I7" s="2" t="n">
         <v>3.71</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="J7" s="2" t="n">
         <v>98.98999999999999</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="K7" s="2" t="n">
         <v>27.62</v>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="L7" s="2" t="n">
         <v>96.09</v>
       </c>
-      <c r="M7" s="5" t="n">
+      <c r="M7" s="2" t="n">
         <v>23.78</v>
       </c>
-      <c r="N7" s="5" t="n">
+      <c r="N7" s="2" t="n">
         <v>96.06999999999999</v>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=None,scale_th=4.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>97.97</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>51.94</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>90.72</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>25.71</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>96.56</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>27.37</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>96.14</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>96.11</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=None,scale_th=10.0,type=max</t>
         </is>
       </c>
     </row>
